--- a/预测水位/OutputData/SK09.xlsx(out).xlsx
+++ b/预测水位/OutputData/SK09.xlsx(out).xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B2161"/>
+  <dimension ref="A1:B2317"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -17726,6 +17726,1254 @@
         <v>920.345</v>
       </c>
     </row>
+    <row r="2162">
+      <c r="A2162" s="2" t="n">
+        <v>45838</v>
+      </c>
+      <c r="B2162" t="n">
+        <v>920.395</v>
+      </c>
+    </row>
+    <row r="2163">
+      <c r="A2163" s="2" t="n">
+        <v>45838.08333333334</v>
+      </c>
+      <c r="B2163" t="n">
+        <v>920.4355</v>
+      </c>
+    </row>
+    <row r="2164">
+      <c r="A2164" s="2" t="n">
+        <v>45838.16666666666</v>
+      </c>
+      <c r="B2164" t="n">
+        <v>920.476</v>
+      </c>
+    </row>
+    <row r="2165">
+      <c r="A2165" s="2" t="n">
+        <v>45838.25</v>
+      </c>
+      <c r="B2165" t="n">
+        <v>920.502</v>
+      </c>
+    </row>
+    <row r="2166">
+      <c r="A2166" s="2" t="n">
+        <v>45838.33333333334</v>
+      </c>
+      <c r="B2166" t="n">
+        <v>920.527</v>
+      </c>
+    </row>
+    <row r="2167">
+      <c r="A2167" s="2" t="n">
+        <v>45838.41666666666</v>
+      </c>
+      <c r="B2167" t="n">
+        <v>920.548</v>
+      </c>
+    </row>
+    <row r="2168">
+      <c r="A2168" s="2" t="n">
+        <v>45838.5</v>
+      </c>
+      <c r="B2168" t="n">
+        <v>920.564</v>
+      </c>
+    </row>
+    <row r="2169">
+      <c r="A2169" s="2" t="n">
+        <v>45838.58333333334</v>
+      </c>
+      <c r="B2169" t="n">
+        <v>920.58</v>
+      </c>
+    </row>
+    <row r="2170">
+      <c r="A2170" s="2" t="n">
+        <v>45838.66666666666</v>
+      </c>
+      <c r="B2170" t="n">
+        <v>920.593</v>
+      </c>
+    </row>
+    <row r="2171">
+      <c r="A2171" s="2" t="n">
+        <v>45838.75</v>
+      </c>
+      <c r="B2171" t="n">
+        <v>920.615</v>
+      </c>
+    </row>
+    <row r="2172">
+      <c r="A2172" s="2" t="n">
+        <v>45838.83333333334</v>
+      </c>
+      <c r="B2172" t="n">
+        <v>920.633</v>
+      </c>
+    </row>
+    <row r="2173">
+      <c r="A2173" s="2" t="n">
+        <v>45838.91666666666</v>
+      </c>
+      <c r="B2173" t="n">
+        <v>920.646</v>
+      </c>
+    </row>
+    <row r="2174">
+      <c r="A2174" s="2" t="n">
+        <v>45839</v>
+      </c>
+      <c r="B2174" t="n">
+        <v>920.651</v>
+      </c>
+    </row>
+    <row r="2175">
+      <c r="A2175" s="2" t="n">
+        <v>45839.08333333334</v>
+      </c>
+      <c r="B2175" t="n">
+        <v>920.648</v>
+      </c>
+    </row>
+    <row r="2176">
+      <c r="A2176" s="2" t="n">
+        <v>45839.16666666666</v>
+      </c>
+      <c r="B2176" t="n">
+        <v>920.633</v>
+      </c>
+    </row>
+    <row r="2177">
+      <c r="A2177" s="2" t="n">
+        <v>45839.25</v>
+      </c>
+      <c r="B2177" t="n">
+        <v>920.621</v>
+      </c>
+    </row>
+    <row r="2178">
+      <c r="A2178" s="2" t="n">
+        <v>45839.33333333334</v>
+      </c>
+      <c r="B2178" t="n">
+        <v>920.611</v>
+      </c>
+    </row>
+    <row r="2179">
+      <c r="A2179" s="2" t="n">
+        <v>45839.41666666666</v>
+      </c>
+      <c r="B2179" t="n">
+        <v>920.601</v>
+      </c>
+    </row>
+    <row r="2180">
+      <c r="A2180" s="2" t="n">
+        <v>45839.5</v>
+      </c>
+      <c r="B2180" t="n">
+        <v>920.582</v>
+      </c>
+    </row>
+    <row r="2181">
+      <c r="A2181" s="2" t="n">
+        <v>45839.58333333334</v>
+      </c>
+      <c r="B2181" t="n">
+        <v>920.556</v>
+      </c>
+    </row>
+    <row r="2182">
+      <c r="A2182" s="2" t="n">
+        <v>45839.66666666666</v>
+      </c>
+      <c r="B2182" t="n">
+        <v>920.533</v>
+      </c>
+    </row>
+    <row r="2183">
+      <c r="A2183" s="2" t="n">
+        <v>45839.75</v>
+      </c>
+      <c r="B2183" t="n">
+        <v>920.5170000000001</v>
+      </c>
+    </row>
+    <row r="2184">
+      <c r="A2184" s="2" t="n">
+        <v>45839.83333333334</v>
+      </c>
+      <c r="B2184" t="n">
+        <v>920.5069999999999</v>
+      </c>
+    </row>
+    <row r="2185">
+      <c r="A2185" s="2" t="n">
+        <v>45839.91666666666</v>
+      </c>
+      <c r="B2185" t="n">
+        <v>920.489</v>
+      </c>
+    </row>
+    <row r="2186">
+      <c r="A2186" s="2" t="n">
+        <v>45840</v>
+      </c>
+      <c r="B2186" t="n">
+        <v>920.467</v>
+      </c>
+    </row>
+    <row r="2187">
+      <c r="A2187" s="2" t="n">
+        <v>45840.08333333334</v>
+      </c>
+      <c r="B2187" t="n">
+        <v>920.4349999999999</v>
+      </c>
+    </row>
+    <row r="2188">
+      <c r="A2188" s="2" t="n">
+        <v>45840.16666666666</v>
+      </c>
+      <c r="B2188" t="n">
+        <v>920.3869999999999</v>
+      </c>
+    </row>
+    <row r="2189">
+      <c r="A2189" s="2" t="n">
+        <v>45840.25</v>
+      </c>
+      <c r="B2189" t="n">
+        <v>920.349</v>
+      </c>
+    </row>
+    <row r="2190">
+      <c r="A2190" s="2" t="n">
+        <v>45840.33333333334</v>
+      </c>
+      <c r="B2190" t="n">
+        <v>920.309</v>
+      </c>
+    </row>
+    <row r="2191">
+      <c r="A2191" s="2" t="n">
+        <v>45840.41666666666</v>
+      </c>
+      <c r="B2191" t="n">
+        <v>920.272</v>
+      </c>
+    </row>
+    <row r="2192">
+      <c r="A2192" s="2" t="n">
+        <v>45840.5</v>
+      </c>
+      <c r="B2192" t="n">
+        <v>920.227</v>
+      </c>
+    </row>
+    <row r="2193">
+      <c r="A2193" s="2" t="n">
+        <v>45840.58333333334</v>
+      </c>
+      <c r="B2193" t="n">
+        <v>920.1849999999999</v>
+      </c>
+    </row>
+    <row r="2194">
+      <c r="A2194" s="2" t="n">
+        <v>45840.66666666666</v>
+      </c>
+      <c r="B2194" t="n">
+        <v>920.138</v>
+      </c>
+    </row>
+    <row r="2195">
+      <c r="A2195" s="2" t="n">
+        <v>45840.75</v>
+      </c>
+      <c r="B2195" t="n">
+        <v>920.106</v>
+      </c>
+    </row>
+    <row r="2196">
+      <c r="A2196" s="2" t="n">
+        <v>45840.83333333334</v>
+      </c>
+      <c r="B2196" t="n">
+        <v>920.08</v>
+      </c>
+    </row>
+    <row r="2197">
+      <c r="A2197" s="2" t="n">
+        <v>45840.91666666666</v>
+      </c>
+      <c r="B2197" t="n">
+        <v>920.052</v>
+      </c>
+    </row>
+    <row r="2198">
+      <c r="A2198" s="2" t="n">
+        <v>45841</v>
+      </c>
+      <c r="B2198" t="n">
+        <v>920.024</v>
+      </c>
+    </row>
+    <row r="2199">
+      <c r="A2199" s="2" t="n">
+        <v>45841.08333333334</v>
+      </c>
+      <c r="B2199" t="n">
+        <v>919.977</v>
+      </c>
+    </row>
+    <row r="2200">
+      <c r="A2200" s="2" t="n">
+        <v>45841.16666666666</v>
+      </c>
+      <c r="B2200" t="n">
+        <v>919.919</v>
+      </c>
+    </row>
+    <row r="2201">
+      <c r="A2201" s="2" t="n">
+        <v>45841.25</v>
+      </c>
+      <c r="B2201" t="n">
+        <v>919.869</v>
+      </c>
+    </row>
+    <row r="2202">
+      <c r="A2202" s="2" t="n">
+        <v>45841.33333333334</v>
+      </c>
+      <c r="B2202" t="n">
+        <v>919.823</v>
+      </c>
+    </row>
+    <row r="2203">
+      <c r="A2203" s="2" t="n">
+        <v>45841.41666666666</v>
+      </c>
+      <c r="B2203" t="n">
+        <v>919.789</v>
+      </c>
+    </row>
+    <row r="2204">
+      <c r="A2204" s="2" t="n">
+        <v>45841.5</v>
+      </c>
+      <c r="B2204" t="n">
+        <v>919.744</v>
+      </c>
+    </row>
+    <row r="2205">
+      <c r="A2205" s="2" t="n">
+        <v>45841.58333333334</v>
+      </c>
+      <c r="B2205" t="n">
+        <v>919.7</v>
+      </c>
+    </row>
+    <row r="2206">
+      <c r="A2206" s="2" t="n">
+        <v>45841.66666666666</v>
+      </c>
+      <c r="B2206" t="n">
+        <v>919.647</v>
+      </c>
+    </row>
+    <row r="2207">
+      <c r="A2207" s="2" t="n">
+        <v>45841.75</v>
+      </c>
+      <c r="B2207" t="n">
+        <v>919.611</v>
+      </c>
+    </row>
+    <row r="2208">
+      <c r="A2208" s="2" t="n">
+        <v>45841.83333333334</v>
+      </c>
+      <c r="B2208" t="n">
+        <v>919.5839999999999</v>
+      </c>
+    </row>
+    <row r="2209">
+      <c r="A2209" s="2" t="n">
+        <v>45841.91666666666</v>
+      </c>
+      <c r="B2209" t="n">
+        <v>919.551</v>
+      </c>
+    </row>
+    <row r="2210">
+      <c r="A2210" s="2" t="n">
+        <v>45842</v>
+      </c>
+      <c r="B2210" t="n">
+        <v>919.514</v>
+      </c>
+    </row>
+    <row r="2211">
+      <c r="A2211" s="2" t="n">
+        <v>45842.08333333334</v>
+      </c>
+      <c r="B2211" t="n">
+        <v>919.472</v>
+      </c>
+    </row>
+    <row r="2212">
+      <c r="A2212" s="2" t="n">
+        <v>45842.16666666666</v>
+      </c>
+      <c r="B2212" t="n">
+        <v>919.4160000000001</v>
+      </c>
+    </row>
+    <row r="2213">
+      <c r="A2213" s="2" t="n">
+        <v>45842.25</v>
+      </c>
+      <c r="B2213" t="n">
+        <v>919.364</v>
+      </c>
+    </row>
+    <row r="2214">
+      <c r="A2214" s="2" t="n">
+        <v>45842.33333333334</v>
+      </c>
+      <c r="B2214" t="n">
+        <v>919.322</v>
+      </c>
+    </row>
+    <row r="2215">
+      <c r="A2215" s="2" t="n">
+        <v>45842.41666666666</v>
+      </c>
+      <c r="B2215" t="n">
+        <v>919.287</v>
+      </c>
+    </row>
+    <row r="2216">
+      <c r="A2216" s="2" t="n">
+        <v>45842.5</v>
+      </c>
+      <c r="B2216" t="n">
+        <v>919.246</v>
+      </c>
+    </row>
+    <row r="2217">
+      <c r="A2217" s="2" t="n">
+        <v>45842.58333333334</v>
+      </c>
+      <c r="B2217" t="n">
+        <v>919.1950000000001</v>
+      </c>
+    </row>
+    <row r="2218">
+      <c r="A2218" s="2" t="n">
+        <v>45842.66666666666</v>
+      </c>
+      <c r="B2218" t="n">
+        <v>919.1420000000001</v>
+      </c>
+    </row>
+    <row r="2219">
+      <c r="A2219" s="2" t="n">
+        <v>45842.75</v>
+      </c>
+      <c r="B2219" t="n">
+        <v>919.096</v>
+      </c>
+    </row>
+    <row r="2220">
+      <c r="A2220" s="2" t="n">
+        <v>45842.83333333334</v>
+      </c>
+      <c r="B2220" t="n">
+        <v>919.067</v>
+      </c>
+    </row>
+    <row r="2221">
+      <c r="A2221" s="2" t="n">
+        <v>45842.91666666666</v>
+      </c>
+      <c r="B2221" t="n">
+        <v>919.048</v>
+      </c>
+    </row>
+    <row r="2222">
+      <c r="A2222" s="2" t="n">
+        <v>45843</v>
+      </c>
+      <c r="B2222" t="n">
+        <v>919.02</v>
+      </c>
+    </row>
+    <row r="2223">
+      <c r="A2223" s="2" t="n">
+        <v>45843.08333333334</v>
+      </c>
+      <c r="B2223" t="n">
+        <v>918.954</v>
+      </c>
+    </row>
+    <row r="2224">
+      <c r="A2224" s="2" t="n">
+        <v>45843.16666666666</v>
+      </c>
+      <c r="B2224" t="n">
+        <v>918.9</v>
+      </c>
+    </row>
+    <row r="2225">
+      <c r="A2225" s="2" t="n">
+        <v>45843.25</v>
+      </c>
+      <c r="B2225" t="n">
+        <v>918.854</v>
+      </c>
+    </row>
+    <row r="2226">
+      <c r="A2226" s="2" t="n">
+        <v>45843.33333333334</v>
+      </c>
+      <c r="B2226" t="n">
+        <v>918.831</v>
+      </c>
+    </row>
+    <row r="2227">
+      <c r="A2227" s="2" t="n">
+        <v>45843.41666666666</v>
+      </c>
+      <c r="B2227" t="n">
+        <v>918.831</v>
+      </c>
+    </row>
+    <row r="2228">
+      <c r="A2228" s="2" t="n">
+        <v>45843.5</v>
+      </c>
+      <c r="B2228" t="n">
+        <v>918.819</v>
+      </c>
+    </row>
+    <row r="2229">
+      <c r="A2229" s="2" t="n">
+        <v>45843.58333333334</v>
+      </c>
+      <c r="B2229" t="n">
+        <v>918.796</v>
+      </c>
+    </row>
+    <row r="2230">
+      <c r="A2230" s="2" t="n">
+        <v>45843.66666666666</v>
+      </c>
+      <c r="B2230" t="n">
+        <v>918.76</v>
+      </c>
+    </row>
+    <row r="2231">
+      <c r="A2231" s="2" t="n">
+        <v>45843.75</v>
+      </c>
+      <c r="B2231" t="n">
+        <v>918.731</v>
+      </c>
+    </row>
+    <row r="2232">
+      <c r="A2232" s="2" t="n">
+        <v>45843.83333333334</v>
+      </c>
+      <c r="B2232" t="n">
+        <v>918.715</v>
+      </c>
+    </row>
+    <row r="2233">
+      <c r="A2233" s="2" t="n">
+        <v>45843.91666666666</v>
+      </c>
+      <c r="B2233" t="n">
+        <v>918.707</v>
+      </c>
+    </row>
+    <row r="2234">
+      <c r="A2234" s="2" t="n">
+        <v>45844</v>
+      </c>
+      <c r="B2234" t="n">
+        <v>918.694</v>
+      </c>
+    </row>
+    <row r="2235">
+      <c r="A2235" s="2" t="n">
+        <v>45844.08333333334</v>
+      </c>
+      <c r="B2235" t="n">
+        <v>918.652</v>
+      </c>
+    </row>
+    <row r="2236">
+      <c r="A2236" s="2" t="n">
+        <v>45844.16666666666</v>
+      </c>
+      <c r="B2236" t="n">
+        <v>918.596</v>
+      </c>
+    </row>
+    <row r="2237">
+      <c r="A2237" s="2" t="n">
+        <v>45844.25</v>
+      </c>
+      <c r="B2237" t="n">
+        <v>918.549</v>
+      </c>
+    </row>
+    <row r="2238">
+      <c r="A2238" s="2" t="n">
+        <v>45844.33333333334</v>
+      </c>
+      <c r="B2238" t="n">
+        <v>918.515</v>
+      </c>
+    </row>
+    <row r="2239">
+      <c r="A2239" s="2" t="n">
+        <v>45844.41666666666</v>
+      </c>
+      <c r="B2239" t="n">
+        <v>918.4880000000001</v>
+      </c>
+    </row>
+    <row r="2240">
+      <c r="A2240" s="2" t="n">
+        <v>45844.5</v>
+      </c>
+      <c r="B2240" t="n">
+        <v>918.46</v>
+      </c>
+    </row>
+    <row r="2241">
+      <c r="A2241" s="2" t="n">
+        <v>45844.58333333334</v>
+      </c>
+      <c r="B2241" t="n">
+        <v>918.417</v>
+      </c>
+    </row>
+    <row r="2242">
+      <c r="A2242" s="2" t="n">
+        <v>45844.66666666666</v>
+      </c>
+      <c r="B2242" t="n">
+        <v>918.367</v>
+      </c>
+    </row>
+    <row r="2243">
+      <c r="A2243" s="2" t="n">
+        <v>45844.75</v>
+      </c>
+      <c r="B2243" t="n">
+        <v>918.3200000000001</v>
+      </c>
+    </row>
+    <row r="2244">
+      <c r="A2244" s="2" t="n">
+        <v>45844.83333333334</v>
+      </c>
+      <c r="B2244" t="n">
+        <v>918.29</v>
+      </c>
+    </row>
+    <row r="2245">
+      <c r="A2245" s="2" t="n">
+        <v>45844.91666666666</v>
+      </c>
+      <c r="B2245" t="n">
+        <v>918.272</v>
+      </c>
+    </row>
+    <row r="2246">
+      <c r="A2246" s="2" t="n">
+        <v>45845</v>
+      </c>
+      <c r="B2246" t="n">
+        <v>918.249</v>
+      </c>
+    </row>
+    <row r="2247">
+      <c r="A2247" s="2" t="n">
+        <v>45845.08333333334</v>
+      </c>
+      <c r="B2247" t="n">
+        <v>918.211</v>
+      </c>
+    </row>
+    <row r="2248">
+      <c r="A2248" s="2" t="n">
+        <v>45845.16666666666</v>
+      </c>
+      <c r="B2248" t="n">
+        <v>918.163</v>
+      </c>
+    </row>
+    <row r="2249">
+      <c r="A2249" s="2" t="n">
+        <v>45845.25</v>
+      </c>
+      <c r="B2249" t="n">
+        <v>918.116</v>
+      </c>
+    </row>
+    <row r="2250">
+      <c r="A2250" s="2" t="n">
+        <v>45845.33333333334</v>
+      </c>
+      <c r="B2250" t="n">
+        <v>918.081</v>
+      </c>
+    </row>
+    <row r="2251">
+      <c r="A2251" s="2" t="n">
+        <v>45845.41666666666</v>
+      </c>
+      <c r="B2251" t="n">
+        <v>918.054</v>
+      </c>
+    </row>
+    <row r="2252">
+      <c r="A2252" s="2" t="n">
+        <v>45845.5</v>
+      </c>
+      <c r="B2252" t="n">
+        <v>922.23</v>
+      </c>
+    </row>
+    <row r="2253">
+      <c r="A2253" s="2" t="n">
+        <v>45845.58333333334</v>
+      </c>
+      <c r="B2253" t="n">
+        <v>922.232</v>
+      </c>
+    </row>
+    <row r="2254">
+      <c r="A2254" s="2" t="n">
+        <v>45845.66666666666</v>
+      </c>
+      <c r="B2254" t="n">
+        <v>922.221</v>
+      </c>
+    </row>
+    <row r="2255">
+      <c r="A2255" s="2" t="n">
+        <v>45845.75</v>
+      </c>
+      <c r="B2255" t="n">
+        <v>922.194</v>
+      </c>
+    </row>
+    <row r="2256">
+      <c r="A2256" s="2" t="n">
+        <v>45845.83333333334</v>
+      </c>
+      <c r="B2256" t="n">
+        <v>922.1660000000001</v>
+      </c>
+    </row>
+    <row r="2257">
+      <c r="A2257" s="2" t="n">
+        <v>45845.91666666666</v>
+      </c>
+      <c r="B2257" t="n">
+        <v>922.139</v>
+      </c>
+    </row>
+    <row r="2258">
+      <c r="A2258" s="2" t="n">
+        <v>45846</v>
+      </c>
+      <c r="B2258" t="n">
+        <v>922.12</v>
+      </c>
+    </row>
+    <row r="2259">
+      <c r="A2259" s="2" t="n">
+        <v>45846.08333333334</v>
+      </c>
+      <c r="B2259" t="n">
+        <v>922.111</v>
+      </c>
+    </row>
+    <row r="2260">
+      <c r="A2260" s="2" t="n">
+        <v>45846.16666666666</v>
+      </c>
+      <c r="B2260" t="n">
+        <v>922.096</v>
+      </c>
+    </row>
+    <row r="2261">
+      <c r="A2261" s="2" t="n">
+        <v>45846.25</v>
+      </c>
+      <c r="B2261" t="n">
+        <v>922.078</v>
+      </c>
+    </row>
+    <row r="2262">
+      <c r="A2262" s="2" t="n">
+        <v>45846.33333333334</v>
+      </c>
+      <c r="B2262" t="n">
+        <v>922.054</v>
+      </c>
+    </row>
+    <row r="2263">
+      <c r="A2263" s="2" t="n">
+        <v>45846.41666666666</v>
+      </c>
+      <c r="B2263" t="n">
+        <v>922.023</v>
+      </c>
+    </row>
+    <row r="2264">
+      <c r="A2264" s="2" t="n">
+        <v>45846.5</v>
+      </c>
+      <c r="B2264" t="n">
+        <v>921.997</v>
+      </c>
+    </row>
+    <row r="2265">
+      <c r="A2265" s="2" t="n">
+        <v>45846.58333333334</v>
+      </c>
+      <c r="B2265" t="n">
+        <v>921.966</v>
+      </c>
+    </row>
+    <row r="2266">
+      <c r="A2266" s="2" t="n">
+        <v>45846.66666666666</v>
+      </c>
+      <c r="B2266" t="n">
+        <v>921.937</v>
+      </c>
+    </row>
+    <row r="2267">
+      <c r="A2267" s="2" t="n">
+        <v>45846.75</v>
+      </c>
+      <c r="B2267" t="n">
+        <v>921.9059999999999</v>
+      </c>
+    </row>
+    <row r="2268">
+      <c r="A2268" s="2" t="n">
+        <v>45846.83333333334</v>
+      </c>
+      <c r="B2268" t="n">
+        <v>921.871</v>
+      </c>
+    </row>
+    <row r="2269">
+      <c r="A2269" s="2" t="n">
+        <v>45846.91666666666</v>
+      </c>
+      <c r="B2269" t="n">
+        <v>921.838</v>
+      </c>
+    </row>
+    <row r="2270">
+      <c r="A2270" s="2" t="n">
+        <v>45847</v>
+      </c>
+      <c r="B2270" t="n">
+        <v>921.806</v>
+      </c>
+    </row>
+    <row r="2271">
+      <c r="A2271" s="2" t="n">
+        <v>45847.08333333334</v>
+      </c>
+      <c r="B2271" t="n">
+        <v>921.778</v>
+      </c>
+    </row>
+    <row r="2272">
+      <c r="A2272" s="2" t="n">
+        <v>45847.16666666666</v>
+      </c>
+      <c r="B2272" t="n">
+        <v>921.751</v>
+      </c>
+    </row>
+    <row r="2273">
+      <c r="A2273" s="2" t="n">
+        <v>45847.25</v>
+      </c>
+      <c r="B2273" t="n">
+        <v>921.723</v>
+      </c>
+    </row>
+    <row r="2274">
+      <c r="A2274" s="2" t="n">
+        <v>45847.33333333334</v>
+      </c>
+      <c r="B2274" t="n">
+        <v>921.694</v>
+      </c>
+    </row>
+    <row r="2275">
+      <c r="A2275" s="2" t="n">
+        <v>45847.41666666666</v>
+      </c>
+      <c r="B2275" t="n">
+        <v>921.6609999999999</v>
+      </c>
+    </row>
+    <row r="2276">
+      <c r="A2276" s="2" t="n">
+        <v>45847.5</v>
+      </c>
+      <c r="B2276" t="n">
+        <v>921.627</v>
+      </c>
+    </row>
+    <row r="2277">
+      <c r="A2277" s="2" t="n">
+        <v>45847.58333333334</v>
+      </c>
+      <c r="B2277" t="n">
+        <v>921.586</v>
+      </c>
+    </row>
+    <row r="2278">
+      <c r="A2278" s="2" t="n">
+        <v>45847.66666666666</v>
+      </c>
+      <c r="B2278" t="n">
+        <v>921.547</v>
+      </c>
+    </row>
+    <row r="2279">
+      <c r="A2279" s="2" t="n">
+        <v>45847.75</v>
+      </c>
+      <c r="B2279" t="n">
+        <v>921.504</v>
+      </c>
+    </row>
+    <row r="2280">
+      <c r="A2280" s="2" t="n">
+        <v>45847.83333333334</v>
+      </c>
+      <c r="B2280" t="n">
+        <v>921.449</v>
+      </c>
+    </row>
+    <row r="2281">
+      <c r="A2281" s="2" t="n">
+        <v>45847.91666666666</v>
+      </c>
+      <c r="B2281" t="n">
+        <v>921.405</v>
+      </c>
+    </row>
+    <row r="2282">
+      <c r="A2282" s="2" t="n">
+        <v>45848</v>
+      </c>
+      <c r="B2282" t="n">
+        <v>921.353</v>
+      </c>
+    </row>
+    <row r="2283">
+      <c r="A2283" s="2" t="n">
+        <v>45848.08333333334</v>
+      </c>
+      <c r="B2283" t="n">
+        <v>921.307</v>
+      </c>
+    </row>
+    <row r="2284">
+      <c r="A2284" s="2" t="n">
+        <v>45848.16666666666</v>
+      </c>
+      <c r="B2284" t="n">
+        <v>921.247</v>
+      </c>
+    </row>
+    <row r="2285">
+      <c r="A2285" s="2" t="n">
+        <v>45848.25</v>
+      </c>
+      <c r="B2285" t="n">
+        <v>921.204</v>
+      </c>
+    </row>
+    <row r="2286">
+      <c r="A2286" s="2" t="n">
+        <v>45848.33333333334</v>
+      </c>
+      <c r="B2286" t="n">
+        <v>921.163</v>
+      </c>
+    </row>
+    <row r="2287">
+      <c r="A2287" s="2" t="n">
+        <v>45848.41666666666</v>
+      </c>
+      <c r="B2287" t="n">
+        <v>921.112</v>
+      </c>
+    </row>
+    <row r="2288">
+      <c r="A2288" s="2" t="n">
+        <v>45848.5</v>
+      </c>
+      <c r="B2288" t="n">
+        <v>921.0599999999999</v>
+      </c>
+    </row>
+    <row r="2289">
+      <c r="A2289" s="2" t="n">
+        <v>45848.58333333334</v>
+      </c>
+      <c r="B2289" t="n">
+        <v>921.001</v>
+      </c>
+    </row>
+    <row r="2290">
+      <c r="A2290" s="2" t="n">
+        <v>45848.66666666666</v>
+      </c>
+      <c r="B2290" t="n">
+        <v>920.944</v>
+      </c>
+    </row>
+    <row r="2291">
+      <c r="A2291" s="2" t="n">
+        <v>45848.75</v>
+      </c>
+      <c r="B2291" t="n">
+        <v>920.883</v>
+      </c>
+    </row>
+    <row r="2292">
+      <c r="A2292" s="2" t="n">
+        <v>45848.83333333334</v>
+      </c>
+      <c r="B2292" t="n">
+        <v>920.829</v>
+      </c>
+    </row>
+    <row r="2293">
+      <c r="A2293" s="2" t="n">
+        <v>45848.91666666666</v>
+      </c>
+      <c r="B2293" t="n">
+        <v>920.771</v>
+      </c>
+    </row>
+    <row r="2294">
+      <c r="A2294" s="2" t="n">
+        <v>45849</v>
+      </c>
+      <c r="B2294" t="n">
+        <v>920.7089999999999</v>
+      </c>
+    </row>
+    <row r="2295">
+      <c r="A2295" s="2" t="n">
+        <v>45849.08333333334</v>
+      </c>
+      <c r="B2295" t="n">
+        <v>920.653</v>
+      </c>
+    </row>
+    <row r="2296">
+      <c r="A2296" s="2" t="n">
+        <v>45849.16666666666</v>
+      </c>
+      <c r="B2296" t="n">
+        <v>920.602</v>
+      </c>
+    </row>
+    <row r="2297">
+      <c r="A2297" s="2" t="n">
+        <v>45849.25</v>
+      </c>
+      <c r="B2297" t="n">
+        <v>920.568</v>
+      </c>
+    </row>
+    <row r="2298">
+      <c r="A2298" s="2" t="n">
+        <v>45849.33333333334</v>
+      </c>
+      <c r="B2298" t="n">
+        <v>920.538</v>
+      </c>
+    </row>
+    <row r="2299">
+      <c r="A2299" s="2" t="n">
+        <v>45849.41666666666</v>
+      </c>
+      <c r="B2299" t="n">
+        <v>920.506</v>
+      </c>
+    </row>
+    <row r="2300">
+      <c r="A2300" s="2" t="n">
+        <v>45849.5</v>
+      </c>
+      <c r="B2300" t="n">
+        <v>920.456</v>
+      </c>
+    </row>
+    <row r="2301">
+      <c r="A2301" s="2" t="n">
+        <v>45849.58333333334</v>
+      </c>
+      <c r="B2301" t="n">
+        <v>920.394</v>
+      </c>
+    </row>
+    <row r="2302">
+      <c r="A2302" s="2" t="n">
+        <v>45849.66666666666</v>
+      </c>
+      <c r="B2302" t="n">
+        <v>920.343</v>
+      </c>
+    </row>
+    <row r="2303">
+      <c r="A2303" s="2" t="n">
+        <v>45849.75</v>
+      </c>
+      <c r="B2303" t="n">
+        <v>920.3150000000001</v>
+      </c>
+    </row>
+    <row r="2304">
+      <c r="A2304" s="2" t="n">
+        <v>45849.83333333334</v>
+      </c>
+      <c r="B2304" t="n">
+        <v>920.276</v>
+      </c>
+    </row>
+    <row r="2305">
+      <c r="A2305" s="2" t="n">
+        <v>45849.91666666666</v>
+      </c>
+      <c r="B2305" t="n">
+        <v>920.2430000000001</v>
+      </c>
+    </row>
+    <row r="2306">
+      <c r="A2306" s="2" t="n">
+        <v>45850</v>
+      </c>
+      <c r="B2306" t="n">
+        <v>920.1950000000001</v>
+      </c>
+    </row>
+    <row r="2307">
+      <c r="A2307" s="2" t="n">
+        <v>45850.08333333334</v>
+      </c>
+      <c r="B2307" t="n">
+        <v>920.149</v>
+      </c>
+    </row>
+    <row r="2308">
+      <c r="A2308" s="2" t="n">
+        <v>45850.16666666666</v>
+      </c>
+      <c r="B2308" t="n">
+        <v>920.102</v>
+      </c>
+    </row>
+    <row r="2309">
+      <c r="A2309" s="2" t="n">
+        <v>45850.25</v>
+      </c>
+      <c r="B2309" t="n">
+        <v>920.079</v>
+      </c>
+    </row>
+    <row r="2310">
+      <c r="A2310" s="2" t="n">
+        <v>45850.33333333334</v>
+      </c>
+      <c r="B2310" t="n">
+        <v>920.059</v>
+      </c>
+    </row>
+    <row r="2311">
+      <c r="A2311" s="2" t="n">
+        <v>45850.41666666666</v>
+      </c>
+      <c r="B2311" t="n">
+        <v>920.043</v>
+      </c>
+    </row>
+    <row r="2312">
+      <c r="A2312" s="2" t="n">
+        <v>45850.5</v>
+      </c>
+      <c r="B2312" t="n">
+        <v>920.022</v>
+      </c>
+    </row>
+    <row r="2313">
+      <c r="A2313" s="2" t="n">
+        <v>45850.58333333334</v>
+      </c>
+      <c r="B2313" t="n">
+        <v>919.985</v>
+      </c>
+    </row>
+    <row r="2314">
+      <c r="A2314" s="2" t="n">
+        <v>45850.66666666666</v>
+      </c>
+      <c r="B2314" t="n">
+        <v>919.9400000000001</v>
+      </c>
+    </row>
+    <row r="2315">
+      <c r="A2315" s="2" t="n">
+        <v>45850.75</v>
+      </c>
+      <c r="B2315" t="n">
+        <v>919.897</v>
+      </c>
+    </row>
+    <row r="2316">
+      <c r="A2316" s="2" t="n">
+        <v>45850.83333333334</v>
+      </c>
+      <c r="B2316" t="n">
+        <v>919.865</v>
+      </c>
+    </row>
+    <row r="2317">
+      <c r="A2317" s="2" t="n">
+        <v>45850.91666666666</v>
+      </c>
+      <c r="B2317" t="n">
+        <v>919.835</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
